--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,29 +486,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Sr. Infrastructure AI Automation Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,38 +517,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=a554996e94433586</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Redshift, Data Lake, Redshift, Kafka, Hadoop, Tableau, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Research Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,192 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Apache Kafka Developer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OpenShift Administrator</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=212896792882132a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a90c0cbdc0f8dedb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Scientist - Predictive Maintenance</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cutsforth</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9895e4a61b09e914</t>
+          <t>https://www.indeed.com/viewjob?jk=020886bc96db32d8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure AI Automation Consultant</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a554996e94433586</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>Associate DevOps SRE - Warehouse Automation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Opex Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Moorestown, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>RAG, Cortex, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6925c8bd9b2317</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Research Engineer, Institute for Software Integrated Systems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,262 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
+          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Julia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52b7fa561a473e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Research Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Rockhaven Homes, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sandy Springs, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, BigQuery, FastAPI, Git, BigQuery, MySQL, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebb0767279f7fc29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ASTRELUX IT INC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c1453dc1b1c8871</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>11.1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=020886bc96db32d8</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97a9d26bc7613285</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Streaming Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0b96bc3c3177be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supply Chain Advanced Analytics Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e40ae86791f52cec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Python</t>
+          <t>Data Scientist, S3, BigQuery, MLflow, CI/CD, Snowflake, Databricks, BigQuery, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate DevOps SRE - Warehouse Automation</t>
+          <t>Senior Full Stack Engineer – AI &amp; Next.js | Remote (EST&amp;CST) | 10+ years of exp. |</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Opex Corporation</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Moorestown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, Copilot, Prompt Engineering, Kafka, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6925c8bd9b2317</t>
+          <t>https://www.indeed.com/viewjob?jk=3a72cda05f31bcd2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Research Engineer, Institute for Software Integrated Systems</t>
+          <t>Site Reliability Engineer, Pragma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Julia</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52b7fa561a473e</t>
+          <t>https://www.indeed.com/viewjob?jk=b71cd884234121c2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Research Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rockhaven Homes, LLC</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sandy Springs, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, BigQuery, FastAPI, Git, BigQuery, MySQL, Power BI, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb0767279f7fc29</t>
+          <t>https://www.indeed.com/viewjob?jk=ed7450aca8fb8d39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASTRELUX IT INC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,182 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1453dc1b1c8871</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Sr. Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a9d26bc7613285</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Streaming Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b96bc3c3177be5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Supply Chain Advanced Analytics Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kimberly-Clark</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e40ae86791f52cec</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=d83386598c6cfaf5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Nitor Infotech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, AWS SageMaker, Azure ML</t>
+          <t>RAG, S3, EC2, Redshift, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, BigQuery, MLflow, CI/CD, Snowflake, Databricks, BigQuery, PySpark, Kafka</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Kinesis, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – AI &amp; Next.js | Remote (EST&amp;CST) | 10+ years of exp. |</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Copilot, Prompt Engineering, Kafka, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a72cda05f31bcd2</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Pragma</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>RAG, EC2, Glue, Athena, AKS, Terraform, Git, PySpark, MySQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b71cd884234121c2</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Research Engineer</t>
+          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed7450aca8fb8d39</t>
+          <t>https://www.indeed.com/viewjob?jk=98165ff18805045e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,462 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=d8bbccb80ccaab4b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Fullstack</t>
+          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06e96b9eaac8b851</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Payments)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Concord, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Redshift, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Advanced Analytics &amp; Research Specialist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Great American Insurance Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e906494bc8d6945d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Intelligence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, BigQuery, Git, Snowflake, BigQuery, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f041998220dcd6a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Intelligence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, BigQuery, Git, Snowflake, BigQuery, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca51d6eda8f3ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data and Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db60315f99d4aa3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=080944321355f8af</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customers Bank</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Malvern, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d83386598c6cfaf5</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a5d37cf4462f14b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SENIOR CLOUD ENGINEER</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scripps Research</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0dd9aaa9f2147b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08bbb1da8e54cfc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nitor Infotech</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Redshift, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, RAG, XGBoost, CatBoost, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Kinesis, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Entry level Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0b62f6f860ca70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>Full Stack Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, EC2, Glue, Athena, AKS, Terraform, Git, PySpark, MySQL, Python</t>
+          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=4836dbf454cb42c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>QTS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98165ff18805045e</t>
+          <t>https://www.indeed.com/viewjob?jk=240778fbc8fb3be8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
+          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8bbccb80ccaab4b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Quant, Artificial Intelligence/Machine Learning</t>
+          <t>AI Orchestration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e96b9eaac8b851</t>
+          <t>https://www.indeed.com/viewjob?jk=74b3655754596d53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=17640f2697ff3efc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Redshift, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3f20d76a0561f3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advanced Analytics &amp; Research Specialist</t>
+          <t>Software Engineer I - Credit Karma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e906494bc8d6945d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7017d4804ef784a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Intelligence</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, Git, Snowflake, BigQuery, Python, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Redshift, AKS, Git, Snowflake, Redshift, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f041998220dcd6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=19de2381959f2093</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Intelligence</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, Git, Snowflake, BigQuery, Python, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca51d6eda8f3ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60315f99d4aa3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Fullstack Software Engineer- Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>Generative AI, BigQuery, Snowflake, Databricks, BigQuery, NoSQL, Tableau, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080944321355f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=fa4908b2c68c6124</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5d37cf4462f14b</t>
+          <t>https://www.indeed.com/viewjob?jk=9327df072039a82d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SENIOR CLOUD ENGINEER</t>
+          <t>Software Engineer II, Data Management</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scripps Research</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, AWS SageMaker, S3, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,357 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0dd9aaa9f2147b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa64246dac3e40e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>City of Worcester</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Worcester, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hadoop, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dechert LLP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5863bb394c24ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, Kafka, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=021bfbd3e3b2ed27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08bbb1da8e54cfc</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Greenberg Traurig</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6ea315564cf366</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Forward-Deployed Product Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Habitat Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, AKS, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac165276de0dd6cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Forward-Deployed Product Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Habitat Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, AKS, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cbc6c83f6ae75bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DATA ANALYST L3(CONTRACT)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6effce65ce0e19cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Washington State Hospital Association</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Redshift, Snowflake, Redshift, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17bb67698a6b8ce5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, CatBoost, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, RAG, FAISS, XGBoost, LightGBM, Redshift, BigQuery, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, FAISS, XGBoost, LightGBM, Redshift, BigQuery, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Entry level Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilti Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Kinesis, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0b62f6f860ca70</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - AI Applications</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Glue, Athena, Redshift, Docker, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4836dbf454cb42c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QTS</t>
+          <t>MonoSol LLC.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, Git</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, LightGBM, Git, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=240778fbc8fb3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=0faac848da7e4fe6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Copilot, BigQuery, Docker, Apache Airflow, CI/CD, Git, BigQuery, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Orchestration Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Kafka, Python, SQL</t>
+          <t>Data Scientist, RAG, Athena, Redshift, Data Lake, CI/CD, Git, Redshift, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b3655754596d53</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer 2, Merchandise Order Management - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, R</t>
+          <t>Copilot, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17640f2697ff3efc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d06d423e8821ac3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>AI Evaluation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, S3, Glue, MLflow, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=fa921d016588b93c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Mill</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Bruno, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Redshift, BigQuery, CI/CD, Terraform, Snowflake, BigQuery, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3f20d76a0561f3</t>
+          <t>https://www.indeed.com/viewjob?jk=83b14aac9305e4c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer I - Credit Karma</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7017d4804ef784a</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, AKS, Git, Snowflake, Redshift, Power BI, Python, R</t>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19de2381959f2093</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=291e065bfa591afe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Orion Advisor Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Data Lake, CI/CD, Git, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,462 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fullstack Software Engineer- Analytics</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Yoodli AI Roleplays</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, BigQuery, Snowflake, Databricks, BigQuery, NoSQL, Tableau, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa4908b2c68c6124</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Test Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9327df072039a82d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Data Management</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, AWS SageMaker, S3, Git, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa64246dac3e40e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Blue Shield of California</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>City of Worcester</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Hadoop, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Dechert LLP</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5863bb394c24ebf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Publicis Groupe</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>FastAPI, Docker, Kubernetes, Kafka, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=021bfbd3e3b2ed27</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Greenberg Traurig</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6ea315564cf366</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Forward-Deployed Product Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Habitat Health</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, AKS, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac165276de0dd6cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Forward-Deployed Product Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Habitat Health</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, AKS, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbc6c83f6ae75bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DATA ANALYST L3(CONTRACT)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6effce65ce0e19cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Washington State Hospital Association</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Redshift, Snowflake, Redshift, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17bb67698a6b8ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=022c3440d6b72430</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-17.xlsx
+++ b/daily_matches/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FAISS, XGBoost, LightGBM, Redshift, BigQuery, Docker, Kubernetes</t>
+          <t>AI Engineer, LangChain, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FAISS, XGBoost, LightGBM, Redshift, BigQuery, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hilti Group</t>
+          <t>Jacobs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Kinesis, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, Pinecone, Data Lake, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e906691a188517c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Glue, Athena, Redshift, Docker, CI/CD, Terraform</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=06d3ebc80bcfc4cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MonoSol LLC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, LightGBM, Git, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faac848da7e4fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, BigQuery, Docker, Apache Airflow, CI/CD, Git, BigQuery, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Athena, Redshift, Data Lake, CI/CD, Git, Redshift, Kafka, MongoDB</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Order Management - (Hybrid, Seattle)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d06d423e8821ac3</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Evaluation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, S3, Glue, MLflow, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa921d016588b93c</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mill</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Bruno, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, CI/CD, Terraform, Snowflake, BigQuery, Redshift, Tableau, Python</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b14aac9305e4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,987 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291e065bfa591afe</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Orion Advisor Technology</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hazleton, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Florence, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. Java/React FSE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7523ee959e30aea8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Java/React FSE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddfa043b9e204f89</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Consultant, Mobile App Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Travel + Leisure Co.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Quality Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79ca9fa003f87360</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior UX Software Engineer 7.26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GRVTY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UX Software Engineer 6.2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GRVTY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2832f299b10aff54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8975f6247c8e9d02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rand Technology</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a715827e48b85e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - AI Platform</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brivo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c054732756e75e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6248bdf5c9b6fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2cc3c68a19ebf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15e844a1943f6a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, CI/CD, Git, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022c3440d6b72430</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50416c5a26e39513</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>T. Rowe Price</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Snowflake, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Laed Java Full Stack with Struts Modernization</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0e538df070aca9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BIM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53a310e1bbf57a43</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Terraform, Git, Databricks, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ecf80474382f332</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Technology Engineer II – Platform &amp; Full Stack Engineering</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e97e3393e14c2d5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Laed Java Full Stack with Struts Modernization</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38c8a2951e3f278e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Marketing Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Puget Sound Energy</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cccf16d4b27dcf17</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>New Classrooms Innovation Partners Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c950e452fcb9cd79</t>
         </is>
       </c>
     </row>
